--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484249_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484249_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.4307</v>
+        <v>9.8611</v>
       </c>
       <c r="E2" t="n">
-        <v>6.236</v>
+        <v>5.9932</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1948</v>
+        <v>3.8679</v>
       </c>
       <c r="G2" t="n">
         <v>5.6097</v>
@@ -610,13 +610,13 @@
         <v>1.5627</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4108</v>
+        <v>0.8411999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6219</v>
+        <v>0.3791</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7889</v>
+        <v>0.4621</v>
       </c>
       <c r="V2" t="n">
         <v>2.8242</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.719200000000001</v>
+        <v>7.951</v>
       </c>
       <c r="E3" t="n">
-        <v>6.81</v>
+        <v>6.6683</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9092</v>
+        <v>1.2828</v>
       </c>
       <c r="G3" t="n">
         <v>6.4377</v>
@@ -688,13 +688,13 @@
         <v>1.5627</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9374</v>
+        <v>1.1692</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6824</v>
+        <v>0.5407</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2549</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>-1.2186</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.3779</v>
+        <v>6.7182</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5421</v>
+        <v>3.3105</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8358</v>
+        <v>3.4077</v>
       </c>
       <c r="G4" t="n">
         <v>4.1549</v>
@@ -766,13 +766,13 @@
         <v>2.1488</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1677</v>
+        <v>0.1726</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6657</v>
+        <v>0.1026</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5019</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>1.2186</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. RUIZ CAÑAMERO</t>
+          <t>J. SOLE MORGADO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5499</v>
+        <v>3.0077</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7785</v>
+        <v>2.0287</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2286</v>
+        <v>0.979</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7715</v>
+        <v>1.9678</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1238</v>
+        <v>-0.4876</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6476</v>
+        <v>2.4554</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3921</v>
+        <v>1.9874</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2302</v>
+        <v>0.2059</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1619</v>
+        <v>1.7815</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1636</v>
+        <v>-0.0196</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.354</v>
+        <v>-0.6935</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8095</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3093</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>2.7185</v>
+        <v>0.0413</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5908</v>
+        <v>0.0219</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.5507</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. SOLE MORGADO</t>
+          <t>R. CARRASCO SAGRISTA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4883</v>
+        <v>2.3509</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5637</v>
+        <v>0.6171</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9245</v>
+        <v>1.7337</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9678</v>
+        <v>2.8196</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4876</v>
+        <v>2.6846</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4554</v>
+        <v>0.135</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9874</v>
+        <v>2.105</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2059</v>
+        <v>3.318</v>
       </c>
       <c r="L6" t="n">
-        <v>1.7815</v>
+        <v>-1.213</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0196</v>
+        <v>0.7146</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6935</v>
+        <v>-0.6334</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6739000000000001</v>
+        <v>1.348</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9767</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4562</v>
+        <v>0.4298</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4237</v>
+        <v>0.2236</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0326</v>
+        <v>0.2062</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. LLOVET CAMP</t>
+          <t>J. OMOARUNA OSAZUWA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4156</v>
+        <v>1.8999</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1705</v>
+        <v>0.6063</v>
       </c>
       <c r="F7" t="n">
-        <v>1.245</v>
+        <v>1.2936</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7126</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1998</v>
+        <v>1.1653</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5128</v>
+        <v>-0.1749</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4278</v>
+        <v>1.6796</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5897</v>
+        <v>1.045</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1619</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2848</v>
+        <v>-0.6893</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3899</v>
+        <v>0.1203</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6747</v>
+        <v>-0.8095</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1488</v>
+        <v>1.3674</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1488</v>
+        <v>2.3441</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3664</v>
+        <v>0.4836</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4308</v>
+        <v>0.5676</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0645</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3869</v>
+        <v>-0.9414</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1675</v>
+        <v>-0.6642</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5545</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. CARRASCO SAGRISTA</t>
+          <t>I. LLOVET CAMP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4736</v>
+        <v>1.7749</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1512</v>
+        <v>0.5026</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6248</v>
+        <v>1.2723</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8196</v>
+        <v>-0.7126</v>
       </c>
       <c r="H8" t="n">
-        <v>2.6846</v>
+        <v>-0.1998</v>
       </c>
       <c r="I8" t="n">
-        <v>0.135</v>
+        <v>-0.5128</v>
       </c>
       <c r="J8" t="n">
-        <v>2.105</v>
+        <v>-0.4278</v>
       </c>
       <c r="K8" t="n">
-        <v>3.318</v>
+        <v>-0.5897</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.213</v>
+        <v>0.1619</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7146</v>
+        <v>-0.2848</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6334</v>
+        <v>0.3899</v>
       </c>
       <c r="O8" t="n">
-        <v>1.348</v>
+        <v>-0.6747</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.5627</v>
+        <v>2.1488</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3674</v>
+        <v>2.1488</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4475</v>
+        <v>0.7256</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5447</v>
+        <v>0.7629</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0973</v>
+        <v>-0.0373</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6642</v>
+        <v>-0.3869</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2186</v>
+        <v>0.1675</v>
       </c>
       <c r="X8" t="n">
         <v>-0.5545</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. OMOARUNA OSAZUWA</t>
+          <t>M. SESE FRASNEDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2183</v>
+        <v>1.1271</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0609</v>
+        <v>-0.8241000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1574</v>
+        <v>1.9512</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9903999999999999</v>
+        <v>-0.1348</v>
       </c>
       <c r="H9" t="n">
-        <v>1.1653</v>
+        <v>0.5526</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1749</v>
+        <v>-0.6873</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6796</v>
+        <v>0.0102</v>
       </c>
       <c r="K9" t="n">
-        <v>1.045</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6346000000000001</v>
+        <v>-0.6869</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6893</v>
+        <v>-0.1449</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1203</v>
+        <v>-0.1445</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8095</v>
+        <v>-0.0004</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3674</v>
+        <v>0.3907</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3441</v>
+        <v>1.3674</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1981</v>
+        <v>0.207</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0221</v>
+        <v>0.1424</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2202</v>
+        <v>0.0646</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9414</v>
+        <v>0.6642</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2772</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="10">
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.214</v>
+        <v>1.0627</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2139</v>
+        <v>0.6349</v>
       </c>
       <c r="F10" t="n">
         <v>0.4279</v>
@@ -1234,10 +1234,10 @@
         <v>2.3441</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7814</v>
+        <v>0.0674</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.773</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="U10" t="n">
         <v>-0.0083</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. SESE FRASNEDO</t>
+          <t>A. RUIZ CAÑAMERO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1343</v>
+        <v>0.4078</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5718</v>
+        <v>1.0994</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7061</v>
+        <v>-0.6916</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1348</v>
+        <v>-0.7715</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5526</v>
+        <v>-0.1238</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6873</v>
+        <v>-0.6476</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0102</v>
+        <v>0.3921</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6971000000000001</v>
+        <v>0.2302</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6869</v>
+        <v>0.1619</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1449</v>
+        <v>-1.1636</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1445</v>
+        <v>-0.354</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0004</v>
+        <v>-0.8095</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3907</v>
+        <v>1.5627</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3674</v>
+        <v>1.5627</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7858000000000001</v>
+        <v>1.1673</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6052</v>
+        <v>1.0394</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1805</v>
+        <v>0.1278</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6642</v>
+        <v>-1.5507</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X11" t="n">
-        <v>0.6642</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.5508</v>
+        <v>-0.1774</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.794</v>
+        <v>-0.6929</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2432</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>0.8612</v>
@@ -1390,13 +1390,13 @@
         <v>1.1721</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7208</v>
+        <v>-0.3474</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2888</v>
+        <v>-0.1877</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.432</v>
+        <v>-0.1597</v>
       </c>
       <c r="V12" t="n">
         <v>-0.8865</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>34.471</v>
+        <v>35.98390000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>18.4308</v>
+        <v>19.944</v>
       </c>
       <c r="F13" t="n">
         <v>16.0401</v>
@@ -1438,7 +1438,7 @@
         <v>14.2775</v>
       </c>
       <c r="I13" t="n">
-        <v>8.7684</v>
+        <v>8.768399999999998</v>
       </c>
       <c r="J13" t="n">
         <v>22.9189</v>
@@ -1447,19 +1447,19 @@
         <v>16.8431</v>
       </c>
       <c r="L13" t="n">
-        <v>6.075900000000001</v>
+        <v>6.0759</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1267</v>
+        <v>0.1267000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.5655</v>
+        <v>-2.565500000000001</v>
       </c>
       <c r="O13" t="n">
         <v>2.6924</v>
       </c>
       <c r="P13" t="n">
-        <v>8.7904</v>
+        <v>8.790399999999998</v>
       </c>
       <c r="Q13" t="n">
         <v>-9.766999999999999</v>
@@ -1468,19 +1468,19 @@
         <v>18.5575</v>
       </c>
       <c r="S13" t="n">
-        <v>3.466400000000001</v>
+        <v>4.9795</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1746</v>
+        <v>3.6877</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2919</v>
+        <v>1.2918</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.8315</v>
+        <v>-0.8314999999999998</v>
       </c>
       <c r="W13" t="n">
-        <v>3.104299999999999</v>
+        <v>3.1043</v>
       </c>
       <c r="X13" t="n">
         <v>-3.935999999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.302</v>
+        <v>3.3214</v>
       </c>
       <c r="E14" t="n">
-        <v>2.147</v>
+        <v>2.2481</v>
       </c>
       <c r="F14" t="n">
-        <v>1.155</v>
+        <v>1.0733</v>
       </c>
       <c r="G14" t="n">
         <v>2.212</v>
@@ -1546,13 +1546,13 @@
         <v>1.3674</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2774</v>
+        <v>-0.258</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4842</v>
+        <v>-0.3831</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2068</v>
+        <v>0.1251</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2601</v>
+        <v>2.0487</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6695</v>
+        <v>0.5684</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5906</v>
+        <v>1.4803</v>
       </c>
       <c r="G15" t="n">
         <v>1.3747</v>
@@ -1624,13 +1624,13 @@
         <v>1.7581</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6509</v>
+        <v>0.4395</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5339</v>
+        <v>0.4327</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1171</v>
+        <v>0.0068</v>
       </c>
       <c r="V15" t="n">
         <v>-1.3283</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6211</v>
+        <v>-0.2763</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0377</v>
+        <v>0.0634</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5835</v>
+        <v>-0.3397</v>
       </c>
       <c r="G16" t="n">
         <v>-2.182</v>
@@ -1702,13 +1702,13 @@
         <v>0.9767</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4391</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0221</v>
+        <v>0.1232</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4612</v>
+        <v>-0.2175</v>
       </c>
       <c r="V16" t="n">
         <v>1.2186</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X. ALMIRALL CANALS</t>
+          <t>J. MARTIN TRENADO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.14</v>
+        <v>-0.7722</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5101</v>
+        <v>-0.1347</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6299</v>
+        <v>-0.6375</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6726</v>
+        <v>0.3381</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5779</v>
+        <v>-1.2267</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.09470000000000001</v>
+        <v>1.5647</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0814</v>
+        <v>2.065</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0409</v>
+        <v>0.9043</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0405</v>
+        <v>1.1607</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.754</v>
+        <v>-1.7269</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6188</v>
+        <v>-2.131</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1352</v>
+        <v>0.4041</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1721</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1721</v>
+        <v>-3.3208</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.7814</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6499</v>
+        <v>-0.0667</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5806</v>
+        <v>-0.3747</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0693</v>
+        <v>0.308</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0549</v>
+        <v>1.4959</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0549</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. MARTIN TRENADO</t>
+          <t>X. ALMIRALL CANALS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5215</v>
+        <v>-1.3888</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6403</v>
+        <v>-0.8134</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8813</v>
+        <v>-0.5754</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3381</v>
+        <v>-0.6726</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2267</v>
+        <v>-0.5779</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5647</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>2.065</v>
+        <v>0.0814</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9043</v>
+        <v>0.0409</v>
       </c>
       <c r="L18" t="n">
-        <v>1.1607</v>
+        <v>0.0405</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.7269</v>
+        <v>-0.754</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.131</v>
+        <v>-0.6188</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4041</v>
+        <v>-0.1352</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.5395</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.3208</v>
+        <v>-1.1721</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8159999999999999</v>
+        <v>0.401</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8803</v>
+        <v>0.2773</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0643</v>
+        <v>0.1238</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4959</v>
+        <v>0.0549</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.0549</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>M. SEGARRA BAQUES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.5075</v>
+        <v>-3.4568</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3675</v>
+        <v>-1.1906</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1401</v>
+        <v>-2.2662</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.4837</v>
+        <v>-3.03</v>
       </c>
       <c r="H19" t="n">
-        <v>0.07829999999999999</v>
+        <v>-1.5866</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.562</v>
+        <v>-1.4433</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.3853</v>
+        <v>0.3103</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3111</v>
+        <v>0.944</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.6964</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0984</v>
+        <v>-3.3403</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2328</v>
+        <v>-2.5306</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1344</v>
+        <v>-0.8097</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.5627</v>
+        <v>-2.1488</v>
       </c>
       <c r="R19" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5073</v>
+        <v>-1.1376</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5806</v>
+        <v>-0.5708</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0733</v>
+        <v>-0.5668</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5545</v>
+        <v>1.8828</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5545</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. SEGARRA BAQUES</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.768</v>
+        <v>-3.5011</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3928</v>
+        <v>-2.4686</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.3752</v>
+        <v>-1.0325</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.03</v>
+        <v>-2.4837</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5866</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.4433</v>
+        <v>-2.562</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3103</v>
+        <v>-1.3853</v>
       </c>
       <c r="K20" t="n">
-        <v>0.944</v>
+        <v>1.3111</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-2.6964</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.3403</v>
+        <v>-1.0984</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.5306</v>
+        <v>-1.2328</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8097</v>
+        <v>0.1344</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1488</v>
+        <v>-1.5627</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4488</v>
+        <v>0.5138</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.773</v>
+        <v>0.4795</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6758</v>
+        <v>0.0343</v>
       </c>
       <c r="V20" t="n">
-        <v>1.8828</v>
+        <v>-0.5545</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.6642</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.5231</v>
+        <v>-4.6865</v>
       </c>
       <c r="E21" t="n">
         <v>-0.5586</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.9645</v>
+        <v>-4.1279</v>
       </c>
       <c r="G21" t="n">
         <v>-4.6984</v>
@@ -2092,13 +2092,13 @@
         <v>1.1721</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6015</v>
+        <v>-0.7649</v>
       </c>
       <c r="T21" t="n">
         <v>-0.1594</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.442</v>
+        <v>-0.6054</v>
       </c>
       <c r="V21" t="n">
         <v>0.7768</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. SOLE PIE</t>
+          <t>Q. BARDÉS BADIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.104</v>
+        <v>-5.0436</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2207</v>
+        <v>-2.4946</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.8833</v>
+        <v>-2.549</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.4387</v>
+        <v>-2.0699</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.6311</v>
+        <v>-0.9908</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.8075</v>
+        <v>-1.0792</v>
       </c>
       <c r="J22" t="n">
-        <v>0.251</v>
+        <v>-0.5718</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8442</v>
+        <v>0.1023</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.6741</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.6897</v>
+        <v>-1.4982</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.4753</v>
+        <v>-1.0931</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.2144</v>
+        <v>-0.4051</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.1488</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.3441</v>
+        <v>-1.3674</v>
       </c>
       <c r="R22" t="n">
         <v>0.1953</v>
       </c>
       <c r="S22" t="n">
-        <v>1.0379</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>0.8724</v>
+        <v>0.1087</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1655</v>
+        <v>-0.0275</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5545</v>
+        <v>-1.8828</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5545</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>Q. ROIG GARCIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.3548</v>
+        <v>-5.1277</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6968</v>
+        <v>-2.8945</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.658</v>
+        <v>-2.2333</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.0699</v>
+        <v>-4.3897</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.9908</v>
+        <v>-3.1625</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.0792</v>
+        <v>-1.2272</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5718</v>
+        <v>-1.5836</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1023</v>
+        <v>-1.5708</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6741</v>
+        <v>-0.0128</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.4982</v>
+        <v>-2.8061</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.0931</v>
+        <v>-1.5917</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4051</v>
+        <v>-1.2144</v>
       </c>
       <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>-1.1721</v>
       </c>
-      <c r="Q23" t="n">
-        <v>-1.3674</v>
-      </c>
       <c r="R23" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.23</v>
+        <v>-0.4608</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0935</v>
+        <v>-0.1388</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1365</v>
+        <v>-0.322</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.8828</v>
+        <v>-0.2772</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Q. ROIG GARCIA</t>
+          <t>J. SOLE PIE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.6282</v>
+        <v>-6.298</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.0967</v>
+        <v>-2.333</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.5315</v>
+        <v>-3.965</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.3897</v>
+        <v>-3.4387</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.1625</v>
+        <v>-1.6311</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.2272</v>
+        <v>-1.8075</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.5836</v>
+        <v>0.251</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.5708</v>
+        <v>0.8442</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.0128</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.8061</v>
+        <v>-3.6897</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.5917</v>
+        <v>-2.4753</v>
       </c>
       <c r="O24" t="n">
         <v>-1.2144</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1721</v>
+        <v>-2.3441</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9613</v>
+        <v>-0.1561</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.341</v>
+        <v>-0.2399</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6203</v>
+        <v>0.0838</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.2772</v>
+        <v>-0.5545</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.2772</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.864800000000001</v>
+        <v>-8.6159</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.3355</v>
+        <v>-6.0321</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.5293</v>
+        <v>-2.5838</v>
       </c>
       <c r="G25" t="n">
         <v>-4.0054</v>
@@ -2404,13 +2404,13 @@
         <v>0.586</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.5385</v>
+        <v>-1.2897</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.1499</v>
+        <v>-0.8466</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3886</v>
+        <v>-0.4431</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-34.4709</v>
+        <v>-33.7968</v>
       </c>
       <c r="E26" t="n">
         <v>-16.0402</v>
       </c>
       <c r="F26" t="n">
-        <v>-18.431</v>
+        <v>-17.7567</v>
       </c>
       <c r="G26" t="n">
         <v>-23.0456</v>
@@ -2452,13 +2452,13 @@
         <v>-14.2775</v>
       </c>
       <c r="I26" t="n">
-        <v>-8.7683</v>
+        <v>-8.768300000000002</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.1268000000000002</v>
+        <v>-0.1268000000000005</v>
       </c>
       <c r="K26" t="n">
-        <v>2.565699999999999</v>
+        <v>2.5657</v>
       </c>
       <c r="L26" t="n">
         <v>-2.6925</v>
@@ -2482,19 +2482,19 @@
         <v>9.767099999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.4666</v>
+        <v>-2.7925</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.2917</v>
+        <v>-1.2919</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.1747</v>
+        <v>-1.5005</v>
       </c>
       <c r="V26" t="n">
-        <v>0.8316999999999998</v>
+        <v>0.8317000000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>3.9361</v>
+        <v>3.936100000000001</v>
       </c>
       <c r="X26" t="n">
         <v>-3.1043</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484249_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484249_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>1.3283</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484249_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484249_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484249_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484249_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484249_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,11 +1047,16 @@
       <c r="X7" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484249_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. LLOVET CAMP</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7749</v>
+        <v>1.8279</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5026</v>
+        <v>1.8279</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2723</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7126</v>
+        <v>1.8279</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1998</v>
+        <v>0.614</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5128</v>
+        <v>1.214</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4278</v>
+        <v>1.8279</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5897</v>
+        <v>0.614</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1619</v>
+        <v>1.214</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2848</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3899</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6747</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1488</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1488</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7256</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7629</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0373</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1675</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484249_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. SESE FRASNEDO</t>
+          <t>I. LLOVET CAMP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1271</v>
+        <v>1.7749</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8241000000000001</v>
+        <v>0.5026</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9512</v>
+        <v>1.2723</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1348</v>
+        <v>-0.7126</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5526</v>
+        <v>-0.1998</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6873</v>
+        <v>-0.5128</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0102</v>
+        <v>-0.4278</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6971000000000001</v>
+        <v>-0.5897</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6869</v>
+        <v>0.1619</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1449</v>
+        <v>-0.2848</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1445</v>
+        <v>0.3899</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0004</v>
+        <v>-0.6747</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3907</v>
+        <v>2.1488</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3674</v>
+        <v>2.1488</v>
       </c>
       <c r="S9" t="n">
-        <v>0.207</v>
+        <v>0.7256</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1424</v>
+        <v>0.7629</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0646</v>
+        <v>-0.0373</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6642</v>
+        <v>-0.3869</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.1675</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6642</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484249_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>M. SESE FRASNEDO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0627</v>
+        <v>1.1271</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6349</v>
+        <v>-0.8241000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4279</v>
+        <v>1.9512</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8233</v>
+        <v>-0.1348</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9184</v>
+        <v>0.5526</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9049</v>
+        <v>-0.6873</v>
       </c>
       <c r="J10" t="n">
-        <v>2.5125</v>
+        <v>0.0102</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7982</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>1.7144</v>
+        <v>-0.6869</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6893</v>
+        <v>-0.1449</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1203</v>
+        <v>-0.1445</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8095</v>
+        <v>-0.0004</v>
       </c>
       <c r="P10" t="n">
         <v>0.3907</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3441</v>
+        <v>1.3674</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0674</v>
+        <v>0.207</v>
       </c>
       <c r="T10" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.1424</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0083</v>
+        <v>0.0646</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2186</v>
+        <v>0.6642</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2186</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484249_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. RUIZ CAÑAMERO</t>
+          <t>A. RUIZ CANAMERO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1328,6 +1378,11 @@
       </c>
       <c r="X11" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484249_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1407,11 +1462,16 @@
       <c r="X12" t="n">
         <v>-0.8865</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484249_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,151 +1483,157 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>35.98390000000001</v>
+        <v>-0.7652</v>
       </c>
       <c r="E13" t="n">
-        <v>19.944</v>
+        <v>-1.1931</v>
       </c>
       <c r="F13" t="n">
-        <v>16.0401</v>
+        <v>0.4279</v>
       </c>
       <c r="G13" t="n">
-        <v>23.0457</v>
+        <v>-0.0047</v>
       </c>
       <c r="H13" t="n">
-        <v>14.2775</v>
+        <v>0.3044</v>
       </c>
       <c r="I13" t="n">
-        <v>8.768399999999998</v>
+        <v>-0.3091</v>
       </c>
       <c r="J13" t="n">
-        <v>22.9189</v>
+        <v>0.6846</v>
       </c>
       <c r="K13" t="n">
-        <v>16.8431</v>
+        <v>0.1842</v>
       </c>
       <c r="L13" t="n">
-        <v>6.0759</v>
+        <v>0.5004</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1267000000000001</v>
+        <v>-0.6893</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.565500000000001</v>
+        <v>0.1203</v>
       </c>
       <c r="O13" t="n">
-        <v>2.6924</v>
+        <v>-0.8095</v>
       </c>
       <c r="P13" t="n">
-        <v>8.790399999999998</v>
+        <v>0.3907</v>
       </c>
       <c r="Q13" t="n">
-        <v>-9.766999999999999</v>
+        <v>-1.9534</v>
       </c>
       <c r="R13" t="n">
-        <v>18.5575</v>
+        <v>2.3441</v>
       </c>
       <c r="S13" t="n">
-        <v>4.9795</v>
+        <v>0.0674</v>
       </c>
       <c r="T13" t="n">
-        <v>3.6877</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2918</v>
+        <v>-0.0083</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.8314999999999998</v>
+        <v>-1.2186</v>
       </c>
       <c r="W13" t="n">
-        <v>3.1043</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.935999999999999</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484249_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E. VERA CUSCOLL</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TENEA-C.B. ESPARREGUERA</t>
+          <t>TQ-CB PRAT</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3214</v>
+        <v>35.9839</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2481</v>
+        <v>19.9439</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0733</v>
+        <v>16.0401</v>
       </c>
       <c r="G14" t="n">
-        <v>2.212</v>
+        <v>23.0456</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8764</v>
+        <v>14.2775</v>
       </c>
       <c r="I14" t="n">
-        <v>3.0884</v>
+        <v>8.768399999999998</v>
       </c>
       <c r="J14" t="n">
-        <v>2.6312</v>
+        <v>22.9189</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0819</v>
+        <v>16.8431</v>
       </c>
       <c r="L14" t="n">
-        <v>2.5493</v>
+        <v>6.075900000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4192</v>
+        <v>0.1266999999999998</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9583</v>
+        <v>-2.5655</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5391</v>
+        <v>2.6924</v>
       </c>
       <c r="P14" t="n">
-        <v>1.3674</v>
+        <v>8.7904</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-9.766999999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3674</v>
+        <v>18.5575</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.258</v>
+        <v>4.9795</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3831</v>
+        <v>3.6877</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1251</v>
+        <v>1.2918</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-0.8314999999999998</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.1043</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
-      </c>
+        <v>-3.935999999999999</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. ROSADO FORNIES</t>
+          <t>E. VERA CUSCOLL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0487</v>
+        <v>3.3214</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5684</v>
+        <v>2.2481</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4803</v>
+        <v>1.0733</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3747</v>
+        <v>2.212</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7549</v>
+        <v>-0.8764</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6198</v>
+        <v>3.0884</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6593</v>
+        <v>2.6312</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5784</v>
+        <v>0.0819</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0809</v>
+        <v>2.5493</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2846</v>
+        <v>-0.4192</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8235</v>
+        <v>-0.9583</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5389</v>
+        <v>0.5391</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5627</v>
+        <v>1.3674</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4395</v>
+        <v>-0.258</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4327</v>
+        <v>-0.3831</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0068</v>
+        <v>0.1251</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.3283</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-1.3283</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484249_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. ESTEVES-GARCIA COFFI</t>
+          <t>M. ROSADO FORNIES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2763</v>
+        <v>2.0487</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0634</v>
+        <v>0.5684</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3397</v>
+        <v>1.4803</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.182</v>
+        <v>1.3747</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.779</v>
+        <v>0.7549</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.4031</v>
+        <v>0.6198</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.0831</v>
+        <v>1.6593</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.4899</v>
+        <v>1.5784</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.0809</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.099</v>
+        <v>-0.2846</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2891</v>
+        <v>-0.8235</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8099</v>
+        <v>0.5389</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7814</v>
+        <v>1.5627</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.1953</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9767</v>
+        <v>1.7581</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.09420000000000001</v>
+        <v>0.4395</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1232</v>
+        <v>0.4327</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2175</v>
+        <v>0.0068</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2186</v>
+        <v>-1.3283</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2186</v>
+        <v>-1.3283</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484249_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. MARTIN TRENADO</t>
+          <t>S. ESTEVES-GARCIA COFFI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7722</v>
+        <v>-0.2763</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1347</v>
+        <v>0.0634</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6375</v>
+        <v>-0.3397</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3381</v>
+        <v>-2.182</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2267</v>
+        <v>-0.779</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5647</v>
+        <v>-1.4031</v>
       </c>
       <c r="J17" t="n">
-        <v>2.065</v>
+        <v>-1.0831</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9043</v>
+        <v>-0.4899</v>
       </c>
       <c r="L17" t="n">
-        <v>1.1607</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7269</v>
+        <v>-1.099</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.131</v>
+        <v>-0.2891</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4041</v>
+        <v>-0.8099</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.5395</v>
+        <v>0.7814</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.3208</v>
+        <v>-0.1953</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0667</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3747</v>
+        <v>0.1232</v>
       </c>
       <c r="U17" t="n">
-        <v>0.308</v>
+        <v>-0.2175</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4959</v>
+        <v>1.2186</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4959</v>
+        <v>1.2186</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484249_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X. ALMIRALL CANALS</t>
+          <t>J. MARTIN TRENADO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3888</v>
+        <v>-0.7722</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8134</v>
+        <v>-0.1347</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5754</v>
+        <v>-0.6375</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6726</v>
+        <v>0.3381</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5779</v>
+        <v>-1.2267</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.09470000000000001</v>
+        <v>1.5647</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0814</v>
+        <v>2.065</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0409</v>
+        <v>0.9043</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0405</v>
+        <v>1.1607</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.754</v>
+        <v>-1.7269</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6188</v>
+        <v>-2.131</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1352</v>
+        <v>0.4041</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1721</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1721</v>
+        <v>-3.3208</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.7814</v>
       </c>
       <c r="S18" t="n">
-        <v>0.401</v>
+        <v>-0.0667</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2773</v>
+        <v>-0.3747</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1238</v>
+        <v>0.308</v>
       </c>
       <c r="V18" t="n">
-        <v>0.0549</v>
+        <v>1.4959</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0549</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484249_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. SEGARRA BAQUES</t>
+          <t>X. ALMIRALL CANALS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.4568</v>
+        <v>-1.3888</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1906</v>
+        <v>-0.8134</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2662</v>
+        <v>-0.5754</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.03</v>
+        <v>-0.6726</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.5866</v>
+        <v>-0.5779</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4433</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3103</v>
+        <v>0.0814</v>
       </c>
       <c r="K19" t="n">
-        <v>0.944</v>
+        <v>0.0409</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.0405</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.3403</v>
+        <v>-0.754</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.5306</v>
+        <v>-0.6188</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8097</v>
+        <v>-0.1352</v>
       </c>
       <c r="P19" t="n">
         <v>-1.1721</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1488</v>
+        <v>-1.1721</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1376</v>
+        <v>0.401</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5708</v>
+        <v>0.2773</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5668</v>
+        <v>0.1238</v>
       </c>
       <c r="V19" t="n">
-        <v>1.8828</v>
+        <v>0.0549</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6642</v>
+        <v>0.0549</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484249_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>M. SEGARRA BAQUES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.5011</v>
+        <v>-3.4568</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4686</v>
+        <v>-1.1906</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0325</v>
+        <v>-2.2662</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.4837</v>
+        <v>-3.03</v>
       </c>
       <c r="H20" t="n">
-        <v>0.07829999999999999</v>
+        <v>-1.5866</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.562</v>
+        <v>-1.4433</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3853</v>
+        <v>0.3103</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3111</v>
+        <v>0.944</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.6964</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0984</v>
+        <v>-3.3403</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2328</v>
+        <v>-2.5306</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1344</v>
+        <v>-0.8097</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.5627</v>
+        <v>-2.1488</v>
       </c>
       <c r="R20" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5138</v>
+        <v>-1.1376</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4795</v>
+        <v>-0.5708</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0343</v>
+        <v>-0.5668</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5545</v>
+        <v>1.8828</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5545</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484249_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. BARQUETS ARIZA</t>
+          <t>P. CAMPANA SOLER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.6865</v>
+        <v>-3.5011</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5586</v>
+        <v>-2.4686</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.1279</v>
+        <v>-1.0325</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.6984</v>
+        <v>-2.4837</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.868</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.8304</v>
+        <v>-2.562</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2225</v>
+        <v>-1.3853</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7188</v>
+        <v>1.3111</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.9414</v>
+        <v>-2.6964</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.4759</v>
+        <v>-1.0984</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.5868</v>
+        <v>-1.2328</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.8891</v>
+        <v>0.1344</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1721</v>
+        <v>-1.5627</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7649</v>
+        <v>0.5138</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1594</v>
+        <v>0.4795</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6054</v>
+        <v>0.0343</v>
       </c>
       <c r="V21" t="n">
-        <v>0.7768</v>
+        <v>-0.5545</v>
       </c>
       <c r="W21" t="n">
-        <v>1.9955</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2186</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484249_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>A. BARQUETS ARIZA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.0436</v>
+        <v>-4.6865</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4946</v>
+        <v>-0.5586</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.549</v>
+        <v>-4.1279</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.0699</v>
+        <v>-4.6984</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9908</v>
+        <v>-0.868</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0792</v>
+        <v>-3.8304</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5718</v>
+        <v>-1.2225</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1023</v>
+        <v>0.7188</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6741</v>
+        <v>-1.9414</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4982</v>
+        <v>-3.4759</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0931</v>
+        <v>-1.5868</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4051</v>
+        <v>-1.8891</v>
       </c>
       <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>-1.1721</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-1.3674</v>
-      </c>
       <c r="R22" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="S22" t="n">
-        <v>0.08119999999999999</v>
+        <v>-0.7649</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1087</v>
+        <v>-0.1594</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0275</v>
+        <v>-0.6054</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.8828</v>
+        <v>0.7768</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6642</v>
+        <v>1.9955</v>
       </c>
       <c r="X22" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484249_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Q. ROIG GARCIA</t>
+          <t>Q. BARDES BADIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.1277</v>
+        <v>-5.0436</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8945</v>
+        <v>-2.4946</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2333</v>
+        <v>-2.549</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.3897</v>
+        <v>-2.0699</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.1625</v>
+        <v>-0.9908</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.2272</v>
+        <v>-1.0792</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.5836</v>
+        <v>-0.5718</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.5708</v>
+        <v>0.1023</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.0128</v>
+        <v>-0.6741</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.8061</v>
+        <v>-1.4982</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.5917</v>
+        <v>-1.0931</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.2144</v>
+        <v>-0.4051</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1721</v>
+        <v>-1.3674</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4608</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1388</v>
+        <v>0.1087</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.322</v>
+        <v>-0.0275</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.2772</v>
+        <v>-1.8828</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484249_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. SOLE PIE</t>
+          <t>Q. ROIG GARCIA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.298</v>
+        <v>-5.1277</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.333</v>
+        <v>-2.8945</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.965</v>
+        <v>-2.2333</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.4387</v>
+        <v>-4.3897</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.6311</v>
+        <v>-3.1625</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.8075</v>
+        <v>-1.2272</v>
       </c>
       <c r="J24" t="n">
-        <v>0.251</v>
+        <v>-1.5836</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8442</v>
+        <v>-1.5708</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.0128</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.6897</v>
+        <v>-2.8061</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.4753</v>
+        <v>-1.5917</v>
       </c>
       <c r="O24" t="n">
         <v>-1.2144</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.3441</v>
+        <v>-1.1721</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1561</v>
+        <v>-0.4608</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2399</v>
+        <v>-0.1388</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0838</v>
+        <v>-0.322</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.5545</v>
+        <v>-0.2772</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.5545</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484249_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>J. SOLE PIE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2475,78 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.6159</v>
+        <v>-6.298</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.0321</v>
+        <v>-2.333</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.5838</v>
+        <v>-3.965</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.0054</v>
+        <v>-3.4387</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.4117</v>
+        <v>-1.6311</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5938</v>
+        <v>-1.8075</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.2787</v>
+        <v>0.251</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.8995</v>
+        <v>0.8442</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6208</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.7267</v>
+        <v>-3.6897</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.5121</v>
+        <v>-2.4753</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.2146</v>
+        <v>-1.2144</v>
       </c>
       <c r="P25" t="n">
-        <v>-3.3208</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.9069</v>
+        <v>-2.3441</v>
       </c>
       <c r="R25" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2897</v>
+        <v>-0.1561</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8466</v>
+        <v>-0.2399</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4431</v>
+        <v>0.0838</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484249_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,68 +2558,152 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
+        <v>-8.6159</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-6.0321</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-2.5838</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-4.0054</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-3.4117</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-0.5938</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-1.2787</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-1.8995</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.6208</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-2.7267</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1.5121</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-1.2146</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-3.3208</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-3.9069</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-1.2897</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.8466</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.4431</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484249_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TENEA-C.B. ESPARREGUERA</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
         <v>-33.7968</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E27" t="n">
         <v>-16.0402</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F27" t="n">
         <v>-17.7567</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G27" t="n">
         <v>-23.0456</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H27" t="n">
         <v>-14.2775</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I27" t="n">
         <v>-8.768300000000002</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J27" t="n">
         <v>-0.1268000000000005</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K27" t="n">
         <v>2.5657</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L27" t="n">
         <v>-2.6925</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M27" t="n">
         <v>-22.919</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N27" t="n">
         <v>-16.8431</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O27" t="n">
         <v>-6.0759</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P27" t="n">
         <v>-8.7906</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q27" t="n">
         <v>-18.5576</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R27" t="n">
         <v>9.767099999999999</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S27" t="n">
         <v>-2.7925</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T27" t="n">
         <v>-1.2919</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U27" t="n">
         <v>-1.5005</v>
       </c>
-      <c r="V26" t="n">
+      <c r="V27" t="n">
         <v>0.8317000000000001</v>
       </c>
-      <c r="W26" t="n">
+      <c r="W27" t="n">
         <v>3.936100000000001</v>
       </c>
-      <c r="X26" t="n">
+      <c r="X27" t="n">
         <v>-3.1043</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
